--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486397_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486397_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9694</v>
+        <v>6.6438</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0328</v>
+        <v>2.2757</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9366</v>
+        <v>4.3681</v>
       </c>
       <c r="G2" t="n">
         <v>2.8129</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6769</v>
+        <v>1.3513</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1018</v>
+        <v>1.3447</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4249</v>
+        <v>0.0066</v>
       </c>
       <c r="V2" t="n">
         <v>0.7395</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5394</v>
+        <v>5.5656</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1383</v>
+        <v>5.3186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4011</v>
+        <v>0.247</v>
       </c>
       <c r="G3" t="n">
         <v>5.0904</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1662</v>
+        <v>1.1924</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6802</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4861</v>
+        <v>0.332</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9347</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1906</v>
+        <v>5.4586</v>
       </c>
       <c r="E4" t="n">
-        <v>0.72</v>
+        <v>1.0805</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4706</v>
+        <v>4.3781</v>
       </c>
       <c r="G4" t="n">
         <v>5.6104</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4198</v>
+        <v>-0.1517</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.822</v>
+        <v>-0.4614</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4022</v>
+        <v>0.3097</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4624</v>
+        <v>4.0862</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9019</v>
+        <v>2.5536</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5605</v>
+        <v>1.5326</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5511</v>
+        <v>3.6291</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4818</v>
+        <v>1.9159</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0694</v>
+        <v>1.7132</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4668</v>
+        <v>2.2953</v>
       </c>
       <c r="K5" t="n">
-        <v>1.74</v>
+        <v>0.4777</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7267</v>
+        <v>1.8177</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0844</v>
+        <v>1.3338</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7417</v>
+        <v>1.4382</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3426</v>
+        <v>-0.1044</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.6101</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1288</v>
+        <v>0.3266</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2197</v>
+        <v>-0.1322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9091</v>
+        <v>0.4587</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7395</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1745</v>
+        <v>0.3904</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8297</v>
+        <v>3.398</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0813</v>
+        <v>0.2998</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7484</v>
+        <v>3.0982</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6291</v>
+        <v>3.5511</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9159</v>
+        <v>2.4818</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7132</v>
+        <v>1.0694</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2953</v>
+        <v>2.4668</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4777</v>
+        <v>1.74</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8177</v>
+        <v>0.7267</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3338</v>
+        <v>1.0844</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4382</v>
+        <v>0.7417</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1044</v>
+        <v>0.3426</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.0644</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6044</v>
+        <v>0.6177</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6745</v>
+        <v>0.4467</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7395</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3904</v>
+        <v>-0.1745</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2422</v>
+        <v>1.9302</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0073</v>
+        <v>0.4649</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2495</v>
+        <v>1.4653</v>
       </c>
       <c r="G7" t="n">
         <v>0.2784</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6012</v>
+        <v>0.0868</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3425</v>
+        <v>0.1298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2587</v>
+        <v>-0.043</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0742</v>
+        <v>-0.0886</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7287</v>
+        <v>-2.1073</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8029</v>
+        <v>2.0187</v>
       </c>
       <c r="G8" t="n">
         <v>2.1466</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8204</v>
+        <v>0.6576</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6802</v>
+        <v>0.3016</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1402</v>
+        <v>0.356</v>
       </c>
       <c r="V8" t="n">
         <v>0.3698</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2004</v>
+        <v>-0.4008</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5478</v>
+        <v>-1.6614</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3474</v>
+        <v>1.2605</v>
       </c>
       <c r="G9" t="n">
-        <v>1.641</v>
+        <v>-0.4307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4107</v>
+        <v>-1.7272</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2303</v>
+        <v>1.2965</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3383</v>
+        <v>-1.7335</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.465</v>
+        <v>-2.1558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8032</v>
+        <v>0.4224</v>
       </c>
       <c r="M9" t="n">
         <v>1.3028</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8757</v>
+        <v>0.4286</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4271</v>
+        <v>0.8741</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.6976</v>
+        <v>1.9576</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8562</v>
+        <v>0.3323</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3341</v>
+        <v>0.0721</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5221</v>
+        <v>0.2602</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5483</v>
+        <v>-1.441</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6239</v>
+        <v>-2.6344</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0756</v>
+        <v>1.1933</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4307</v>
+        <v>1.641</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7272</v>
+        <v>0.4107</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2965</v>
+        <v>1.2303</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7335</v>
+        <v>0.3383</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1558</v>
+        <v>-0.465</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4224</v>
+        <v>0.8032</v>
       </c>
       <c r="M10" t="n">
         <v>1.3028</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4286</v>
+        <v>0.8757</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8741</v>
+        <v>0.4271</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9576</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8152</v>
+        <v>0.6156</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8904</v>
+        <v>0.2476</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0752</v>
+        <v>0.368</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6971</v>
+        <v>-1.4976</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.051</v>
+        <v>-0.759</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6461</v>
+        <v>-0.7385</v>
       </c>
       <c r="G11" t="n">
         <v>-0.295</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1422</v>
+        <v>0.0574</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>-0.0505</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2003</v>
+        <v>0.1078</v>
       </c>
       <c r="V11" t="n">
         <v>-1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8179</v>
+        <v>-1.6137</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1106</v>
+        <v>-1.9988</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2927</v>
+        <v>0.3852</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1395</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3734</v>
+        <v>-0.1691</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.114</v>
+        <v>-2.0832</v>
       </c>
       <c r="E13" t="n">
         <v>-1.9011</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2129</v>
+        <v>-0.1821</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8295</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T13" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9302</v>
+        <v>19.9575</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.09610000000000118</v>
+        <v>0.9311000000000011</v>
       </c>
       <c r="F14" t="n">
-        <v>19.0263</v>
+        <v>19.0264</v>
       </c>
       <c r="G14" t="n">
-        <v>23.06519999999999</v>
+        <v>23.0652</v>
       </c>
       <c r="H14" t="n">
         <v>12.7579</v>
@@ -1534,10 +1534,10 @@
         <v>8.087</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8485</v>
+        <v>3.848499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.350000000000001</v>
+        <v>-4.35</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.4003</v>
@@ -1546,16 +1546,16 @@
         <v>13.0503</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1697</v>
+        <v>5.1975</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8087</v>
+        <v>2.8361</v>
       </c>
       <c r="U14" t="n">
         <v>2.3612</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.954800000000001</v>
+        <v>-3.9548</v>
       </c>
       <c r="W14" t="n">
         <v>4.366099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.149</v>
+        <v>3.1419</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9429</v>
+        <v>1.7252</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2061</v>
+        <v>1.4168</v>
       </c>
       <c r="G15" t="n">
         <v>2.9214</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6425</v>
+        <v>-0.6495</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0959</v>
+        <v>-0.3136</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5465</v>
+        <v>-0.3359</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7103</v>
+        <v>1.7977</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6843</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3946</v>
+        <v>2.482</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4661</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0411</v>
+        <v>0.0463</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4194</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3783</v>
+        <v>0.4656</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8005</v>
+        <v>-0.3321</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0526</v>
+        <v>-1.6978</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7479</v>
+        <v>1.3658</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.349</v>
+        <v>0.1654</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1889</v>
+        <v>-0.441</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8399</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8398</v>
+        <v>0.9026</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9545</v>
+        <v>0.7879</v>
       </c>
       <c r="L17" t="n">
         <v>0.1147</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4907</v>
+        <v>-0.7372</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2344</v>
+        <v>-1.2289</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7251</v>
+        <v>0.4916</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9544</v>
+        <v>-0.3022</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3073</v>
+        <v>-0.4254</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6471</v>
+        <v>0.1232</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9347</v>
+        <v>-0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5626</v>
+        <v>-1.3009</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0418</v>
+        <v>-1.7355</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6044</v>
+        <v>0.4346</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2928</v>
+        <v>-0.349</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2282</v>
+        <v>-1.1889</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0646</v>
+        <v>0.8399</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2604</v>
+        <v>-0.8398</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2222</v>
+        <v>-0.9545</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5532</v>
+        <v>0.4907</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4504</v>
+        <v>-0.2344</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1029</v>
+        <v>0.7251</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9026</v>
+        <v>0.8529</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5432</v>
+        <v>0.5191</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3594</v>
+        <v>0.3338</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.9347</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.7602</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.695</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.5443</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.1507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3366</v>
+        <v>-1.6223</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3684</v>
+        <v>-0.7405</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0318</v>
+        <v>-0.8818</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1654</v>
+        <v>-1.2928</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.441</v>
+        <v>-0.2282</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6064000000000001</v>
+        <v>-1.0646</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9026</v>
+        <v>0.2604</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7879</v>
+        <v>0.2222</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7372</v>
+        <v>-1.5532</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2289</v>
+        <v>-0.4504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4916</v>
+        <v>-1.1029</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3067</v>
+        <v>-0.1571</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0959</v>
+        <v>-0.2391</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2108</v>
+        <v>0.082</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-1.1507</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1184</v>
+        <v>-2.0804</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1828</v>
+        <v>-3.4522</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9355</v>
+        <v>1.3719</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8116</v>
+        <v>-4.0009</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3009</v>
+        <v>-0.4589</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1125</v>
+        <v>-3.542</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3589</v>
+        <v>-3.0797</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0547</v>
+        <v>-0.4071</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4136</v>
+        <v>-2.6726</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4528</v>
+        <v>-0.9213</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2461</v>
+        <v>-0.0519</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6989</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2192</v>
+        <v>-0.1643</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2211</v>
+        <v>-0.4999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4403</v>
+        <v>0.3356</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2599</v>
+        <v>3.3899</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.307</v>
+        <v>-2.1335</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2048</v>
+        <v>-1.093</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1022</v>
+        <v>-1.0405</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2231</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1714</v>
+        <v>-0.998</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2019</v>
+        <v>-0.0901</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9695</v>
+        <v>-0.9079</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8665</v>
+        <v>-2.3534</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8993</v>
+        <v>-0.2946</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0328</v>
+        <v>-2.0588</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0009</v>
+        <v>-2.8116</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4589</v>
+        <v>0.3009</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.542</v>
+        <v>-3.1125</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.0797</v>
+        <v>-1.3589</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4071</v>
+        <v>0.0547</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6726</v>
+        <v>-1.4136</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9213</v>
+        <v>-1.4528</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0519</v>
+        <v>0.2461</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8694</v>
+        <v>-1.6989</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9504</v>
+        <v>-0.4542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9469</v>
+        <v>0.1094</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0035</v>
+        <v>-0.5636</v>
       </c>
       <c r="V22" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>3.3899</v>
+        <v>2.2599</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0084</v>
+        <v>-2.7849</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8636</v>
+        <v>-2.6401</v>
       </c>
       <c r="F23" t="n">
         <v>-0.1448</v>
@@ -2248,10 +2248,10 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.709</v>
+        <v>-0.4855</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U23" t="n">
         <v>0.0324</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6407</v>
+        <v>-3.9715</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2942</v>
+        <v>-2.959</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3465</v>
+        <v>-1.0126</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1356</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3752</v>
+        <v>-0.706</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.4062</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6338</v>
+        <v>-0.2998</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7498</v>
+        <v>-6.5456</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5662</v>
+        <v>-5.4545</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1836</v>
+        <v>-1.0912</v>
       </c>
       <c r="G25" t="n">
         <v>-5.2685</v>
@@ -2404,13 +2404,13 @@
         <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6113</v>
+        <v>-0.4071</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1899</v>
+        <v>-0.0781</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4214</v>
+        <v>-0.329</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.9302</v>
+        <v>-18.185</v>
       </c>
       <c r="E26" t="n">
         <v>-19.0263</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09619999999999962</v>
+        <v>0.8413999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-23.0653</v>
@@ -2482,16 +2482,16 @@
         <v>17.4005</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.1698</v>
+        <v>-3.4247</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.3611</v>
+        <v>-2.3612</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8086</v>
+        <v>-1.0636</v>
       </c>
       <c r="V26" t="n">
-        <v>3.9549</v>
+        <v>3.954899999999999</v>
       </c>
       <c r="W26" t="n">
         <v>8.3208</v>
